--- a/Fase 2/Evidencia del Proyecto/Evidencias de documentacion/Metodologia Scrum/Sprint 01234/Sprint 3/Burndown Sprint3 SOC.xlsx
+++ b/Fase 2/Evidencia del Proyecto/Evidencias de documentacion/Metodologia Scrum/Sprint 01234/Sprint 3/Burndown Sprint3 SOC.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\munoz\Desktop\Fase 1\Fase 2\Evidencia del Proyecto\Evidencias de documentacion\Metodologia Scrum\Sprint 01234\Sprint 3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2D30F68E-4A6A-4607-9A47-C747E4D21BE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95EB8A47-1BC0-4806-99E8-27928821AFE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="S2_Burndown" sheetId="3" r:id="rId1"/>
-    <sheet name="S2_Datos" sheetId="1" r:id="rId2"/>
-    <sheet name="S2_Resumen" sheetId="2" r:id="rId3"/>
+    <sheet name="S3_Burndown" sheetId="3" r:id="rId1"/>
+    <sheet name="S3_Datos" sheetId="1" r:id="rId2"/>
+    <sheet name="S3_Resumen" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
@@ -54,10 +54,10 @@
     <t>Objetivo</t>
   </si>
   <si>
-    <t>Sprint 1</t>
-  </si>
-  <si>
     <t>Módulo Gestion operacional</t>
+  </si>
+  <si>
+    <t>Sprint 3</t>
   </si>
 </sst>
 </file>
@@ -204,7 +204,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>S2_Datos!$A$2:$A$16</c:f>
+              <c:f>S3_Datos!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
                 <c:ptCount val="15"/>
@@ -249,7 +249,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>S2_Datos!$B$2:$B$16</c:f>
+              <c:f>S3_Datos!$B$2:$B$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
@@ -314,7 +314,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>S2_Datos!$A$2:$A$16</c:f>
+              <c:f>S3_Datos!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
                 <c:ptCount val="15"/>
@@ -359,7 +359,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>S2_Datos!$C$2:$C$16</c:f>
+              <c:f>S3_Datos!$C$2:$C$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
@@ -1030,7 +1030,7 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -1062,7 +1062,7 @@
         <v>9</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
